--- a/data/nzd0061/nzd0061.xlsx
+++ b/data/nzd0061/nzd0061.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J234"/>
+  <dimension ref="A1:J235"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8860,6 +8860,42 @@
         <v>388.07</v>
       </c>
       <c r="J234" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-20 22:17:54+00:00</t>
+        </is>
+      </c>
+      <c r="B235" t="n">
+        <v>376.6</v>
+      </c>
+      <c r="C235" t="n">
+        <v>357.62</v>
+      </c>
+      <c r="D235" t="n">
+        <v>375.29</v>
+      </c>
+      <c r="E235" t="n">
+        <v>386.71</v>
+      </c>
+      <c r="F235" t="n">
+        <v>391.45</v>
+      </c>
+      <c r="G235" t="n">
+        <v>389.87</v>
+      </c>
+      <c r="H235" t="n">
+        <v>389.67</v>
+      </c>
+      <c r="I235" t="n">
+        <v>388.47</v>
+      </c>
+      <c r="J235" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -8876,7 +8912,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B241"/>
+  <dimension ref="A1:B242"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11289,6 +11325,16 @@
       </c>
       <c r="B241" t="n">
         <v>0.86</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>2025-11-20 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B242" t="n">
+        <v>1.03</v>
       </c>
     </row>
   </sheetData>
@@ -11457,28 +11503,28 @@
         <v>0.0315</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.31677297617397</v>
+        <v>-1.321112096645516</v>
       </c>
       <c r="J2" t="n">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K2" t="n">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2956214858892257</v>
+        <v>0.2989047076770769</v>
       </c>
       <c r="M2" t="n">
-        <v>11.82745496250678</v>
+        <v>11.79751427827906</v>
       </c>
       <c r="N2" t="n">
-        <v>245.6869196522792</v>
+        <v>244.7535052745317</v>
       </c>
       <c r="O2" t="n">
-        <v>15.67440332683446</v>
+        <v>15.64459987582079</v>
       </c>
       <c r="P2" t="n">
-        <v>416.4424182747273</v>
+        <v>416.4838052187429</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -11535,28 +11581,28 @@
         <v>0.0697</v>
       </c>
       <c r="I3" t="n">
-        <v>-2.286344911325281</v>
+        <v>-2.282830825080344</v>
       </c>
       <c r="J3" t="n">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K3" t="n">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="L3" t="n">
-        <v>0.641316302047118</v>
+        <v>0.6427173078797348</v>
       </c>
       <c r="M3" t="n">
-        <v>10.25782343830369</v>
+        <v>10.24004224890249</v>
       </c>
       <c r="N3" t="n">
-        <v>173.8653240984377</v>
+        <v>173.1987388847837</v>
       </c>
       <c r="O3" t="n">
-        <v>13.18580009322292</v>
+        <v>13.16049918828248</v>
       </c>
       <c r="P3" t="n">
-        <v>413.3992872610707</v>
+        <v>413.3657695720277</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -11613,28 +11659,28 @@
         <v>0.0522</v>
       </c>
       <c r="I4" t="n">
-        <v>-2.279807928848415</v>
+        <v>-2.276547512780996</v>
       </c>
       <c r="J4" t="n">
+        <v>234</v>
+      </c>
+      <c r="K4" t="n">
         <v>233</v>
       </c>
-      <c r="K4" t="n">
-        <v>232</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.6671257701211097</v>
+        <v>0.6685283706535216</v>
       </c>
       <c r="M4" t="n">
-        <v>9.769370454255338</v>
+        <v>9.748257079159771</v>
       </c>
       <c r="N4" t="n">
-        <v>153.7127998442424</v>
+        <v>153.1186617053667</v>
       </c>
       <c r="O4" t="n">
-        <v>12.3980966218304</v>
+        <v>12.37411256233621</v>
       </c>
       <c r="P4" t="n">
-        <v>431.2287696691733</v>
+        <v>431.1975355467403</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -11691,28 +11737,28 @@
         <v>0.0455</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.976569732739381</v>
+        <v>-1.97767677551132</v>
       </c>
       <c r="J5" t="n">
+        <v>234</v>
+      </c>
+      <c r="K5" t="n">
         <v>233</v>
       </c>
-      <c r="K5" t="n">
-        <v>232</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.6316190854802317</v>
+        <v>0.6340998700925183</v>
       </c>
       <c r="M5" t="n">
-        <v>9.047569282743007</v>
+        <v>9.013780440870157</v>
       </c>
       <c r="N5" t="n">
-        <v>135.0539263885046</v>
+        <v>134.4818556113153</v>
       </c>
       <c r="O5" t="n">
-        <v>11.62127042919596</v>
+        <v>11.59663121821658</v>
       </c>
       <c r="P5" t="n">
-        <v>439.9553228992167</v>
+        <v>439.9659281436894</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -11769,28 +11815,28 @@
         <v>0.0311</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.519188708699529</v>
+        <v>-1.524899108501383</v>
       </c>
       <c r="J6" t="n">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K6" t="n">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5379757673834419</v>
+        <v>0.5418010152291657</v>
       </c>
       <c r="M6" t="n">
-        <v>8.357586211804339</v>
+        <v>8.353011768405478</v>
       </c>
       <c r="N6" t="n">
-        <v>117.8733452834398</v>
+        <v>117.571434027746</v>
       </c>
       <c r="O6" t="n">
-        <v>10.85694917016009</v>
+        <v>10.84303619968808</v>
       </c>
       <c r="P6" t="n">
-        <v>438.2661608521368</v>
+        <v>438.3206271889109</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -11847,28 +11893,28 @@
         <v>0.0262</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.9466398892416363</v>
+        <v>-0.9529674941852067</v>
       </c>
       <c r="J7" t="n">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K7" t="n">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3491053415567972</v>
+        <v>0.3537632365492198</v>
       </c>
       <c r="M7" t="n">
-        <v>7.684601291132618</v>
+        <v>7.687161496679739</v>
       </c>
       <c r="N7" t="n">
-        <v>99.36053831740718</v>
+        <v>99.18372674358015</v>
       </c>
       <c r="O7" t="n">
-        <v>9.967975637881905</v>
+        <v>9.959102707753352</v>
       </c>
       <c r="P7" t="n">
-        <v>422.395638604104</v>
+        <v>422.4559919022598</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -11925,28 +11971,28 @@
         <v>0.0267</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.8247787530394808</v>
+        <v>-0.8333085852345028</v>
       </c>
       <c r="J8" t="n">
+        <v>234</v>
+      </c>
+      <c r="K8" t="n">
         <v>233</v>
       </c>
-      <c r="K8" t="n">
-        <v>232</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.2769164880643248</v>
+        <v>0.2821478190585546</v>
       </c>
       <c r="M8" t="n">
-        <v>7.395769503816338</v>
+        <v>7.417647670876486</v>
       </c>
       <c r="N8" t="n">
-        <v>105.9655518142268</v>
+        <v>105.9606348209519</v>
       </c>
       <c r="O8" t="n">
-        <v>10.29395705325347</v>
+        <v>10.29371822136937</v>
       </c>
       <c r="P8" t="n">
-        <v>421.635989481415</v>
+        <v>421.7171283879653</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -12003,28 +12049,28 @@
         <v>0.035</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4037786161380548</v>
+        <v>-0.4096509820074042</v>
       </c>
       <c r="J9" t="n">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K9" t="n">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1495945768652835</v>
+        <v>0.154051085680016</v>
       </c>
       <c r="M9" t="n">
-        <v>5.687990364935511</v>
+        <v>5.698078299992304</v>
       </c>
       <c r="N9" t="n">
-        <v>55.11717153280094</v>
+        <v>55.09506005334259</v>
       </c>
       <c r="O9" t="n">
-        <v>7.424093987336161</v>
+        <v>7.422604667725649</v>
       </c>
       <c r="P9" t="n">
-        <v>406.1913835436849</v>
+        <v>406.2473947282251</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -12066,7 +12112,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J234"/>
+  <dimension ref="A1:J235"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24225,6 +24271,58 @@
         </is>
       </c>
     </row>
+    <row r="235">
+      <c r="A235" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-20 22:17:54+00:00</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>-35.17730850876273,173.1179568516578</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>-35.17793150833152,173.11847867984594</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>-35.1782804244542,173.1192755268057</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>-35.17853530265897,173.12008893785222</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>-35.17871419861129,173.1208824255603</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>-35.17880081142662,173.12172767605742</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>-35.1788234048208,173.12259576390764</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>-35.17876489831783,173.12346835064147</t>
+        </is>
+      </c>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0061/nzd0061.xlsx
+++ b/data/nzd0061/nzd0061.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J235"/>
+  <dimension ref="A1:J237"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8898,6 +8898,78 @@
       <c r="J235" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:17:51+00:00</t>
+        </is>
+      </c>
+      <c r="B236" t="n">
+        <v>378.5</v>
+      </c>
+      <c r="C236" t="n">
+        <v>358.28</v>
+      </c>
+      <c r="D236" t="n">
+        <v>376.09</v>
+      </c>
+      <c r="E236" t="n">
+        <v>387.85</v>
+      </c>
+      <c r="F236" t="n">
+        <v>392.98</v>
+      </c>
+      <c r="G236" t="n">
+        <v>391.13</v>
+      </c>
+      <c r="H236" t="n">
+        <v>391.29</v>
+      </c>
+      <c r="I236" t="n">
+        <v>389.37</v>
+      </c>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-14 22:17:57+00:00</t>
+        </is>
+      </c>
+      <c r="B237" t="n">
+        <v>378.65</v>
+      </c>
+      <c r="C237" t="n">
+        <v>355.42</v>
+      </c>
+      <c r="D237" t="n">
+        <v>376.38</v>
+      </c>
+      <c r="E237" t="n">
+        <v>388.37</v>
+      </c>
+      <c r="F237" t="n">
+        <v>393.23</v>
+      </c>
+      <c r="G237" t="n">
+        <v>390.42</v>
+      </c>
+      <c r="H237" t="n">
+        <v>390.04</v>
+      </c>
+      <c r="I237" t="n">
+        <v>388.79</v>
+      </c>
+      <c r="J237" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -8912,7 +8984,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B242"/>
+  <dimension ref="A1:B244"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11335,6 +11407,26 @@
       </c>
       <c r="B242" t="n">
         <v>1.03</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B243" t="n">
+        <v>1.43</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>2025-12-14 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B244" t="n">
+        <v>-0.54</v>
       </c>
     </row>
   </sheetData>
@@ -11503,28 +11595,28 @@
         <v>0.0315</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.321112096645516</v>
+        <v>-1.326177771598281</v>
       </c>
       <c r="J2" t="n">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="K2" t="n">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2989047076770769</v>
+        <v>0.3044262312612459</v>
       </c>
       <c r="M2" t="n">
-        <v>11.79751427827906</v>
+        <v>11.72124461491661</v>
       </c>
       <c r="N2" t="n">
-        <v>244.7535052745317</v>
+        <v>242.7606781941014</v>
       </c>
       <c r="O2" t="n">
-        <v>15.64459987582079</v>
+        <v>15.58077912667083</v>
       </c>
       <c r="P2" t="n">
-        <v>416.4838052187429</v>
+        <v>416.532245236909</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -11581,28 +11673,28 @@
         <v>0.0697</v>
       </c>
       <c r="I3" t="n">
-        <v>-2.282830825080344</v>
+        <v>-2.277089737919934</v>
       </c>
       <c r="J3" t="n">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="K3" t="n">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6427173078797348</v>
+        <v>0.6457313463274553</v>
       </c>
       <c r="M3" t="n">
-        <v>10.24004224890249</v>
+        <v>10.19532519965489</v>
       </c>
       <c r="N3" t="n">
-        <v>173.1987388847837</v>
+        <v>171.8521139668584</v>
       </c>
       <c r="O3" t="n">
-        <v>13.16049918828248</v>
+        <v>13.10923773401255</v>
       </c>
       <c r="P3" t="n">
-        <v>413.3657695720277</v>
+        <v>413.3108815021964</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -11659,28 +11751,28 @@
         <v>0.0522</v>
       </c>
       <c r="I4" t="n">
-        <v>-2.276547512780996</v>
+        <v>-2.268530472534846</v>
       </c>
       <c r="J4" t="n">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="K4" t="n">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6685283706535216</v>
+        <v>0.6708506558472733</v>
       </c>
       <c r="M4" t="n">
-        <v>9.748257079159771</v>
+        <v>9.716271808212191</v>
       </c>
       <c r="N4" t="n">
-        <v>153.1186617053667</v>
+        <v>152.0186725784402</v>
       </c>
       <c r="O4" t="n">
-        <v>12.37411256233621</v>
+        <v>12.32958525573509</v>
       </c>
       <c r="P4" t="n">
-        <v>431.1975355467403</v>
+        <v>431.1205356913031</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -11737,28 +11829,28 @@
         <v>0.0455</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.97767677551132</v>
+        <v>-1.97736656639898</v>
       </c>
       <c r="J5" t="n">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="K5" t="n">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6340998700925183</v>
+        <v>0.6383976268454881</v>
       </c>
       <c r="M5" t="n">
-        <v>9.013780440870157</v>
+        <v>8.939657317518376</v>
       </c>
       <c r="N5" t="n">
-        <v>134.4818556113153</v>
+        <v>133.3383072682641</v>
       </c>
       <c r="O5" t="n">
-        <v>11.59663121821658</v>
+        <v>11.54722075948425</v>
       </c>
       <c r="P5" t="n">
-        <v>439.9659281436894</v>
+        <v>439.9629464957616</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -11815,28 +11907,28 @@
         <v>0.0311</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.524899108501383</v>
+        <v>-1.533107403349669</v>
       </c>
       <c r="J6" t="n">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="K6" t="n">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5418010152291657</v>
+        <v>0.5486934645113961</v>
       </c>
       <c r="M6" t="n">
-        <v>8.353011768405478</v>
+        <v>8.328084901891518</v>
       </c>
       <c r="N6" t="n">
-        <v>117.571434027746</v>
+        <v>116.7886736035045</v>
       </c>
       <c r="O6" t="n">
-        <v>10.84303619968808</v>
+        <v>10.80688084525338</v>
       </c>
       <c r="P6" t="n">
-        <v>438.3206271889109</v>
+        <v>438.3991181998614</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -11893,28 +11985,28 @@
         <v>0.0262</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.9529674941852067</v>
+        <v>-0.9636213816129865</v>
       </c>
       <c r="J7" t="n">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="K7" t="n">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3537632365492198</v>
+        <v>0.3623751057025871</v>
       </c>
       <c r="M7" t="n">
-        <v>7.687161496679739</v>
+        <v>7.682476198283732</v>
       </c>
       <c r="N7" t="n">
-        <v>99.18372674358015</v>
+        <v>98.70371396527656</v>
       </c>
       <c r="O7" t="n">
-        <v>9.959102707753352</v>
+        <v>9.934974281057629</v>
       </c>
       <c r="P7" t="n">
-        <v>422.4559919022598</v>
+        <v>422.5578729558416</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -11971,28 +12063,28 @@
         <v>0.0267</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.8333085852345028</v>
+        <v>-0.8480618515906057</v>
       </c>
       <c r="J8" t="n">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="K8" t="n">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2821478190585546</v>
+        <v>0.2918674017891483</v>
       </c>
       <c r="M8" t="n">
-        <v>7.417647670876486</v>
+        <v>7.446212350985872</v>
       </c>
       <c r="N8" t="n">
-        <v>105.9606348209519</v>
+        <v>105.750882515089</v>
       </c>
       <c r="O8" t="n">
-        <v>10.29371822136937</v>
+        <v>10.28352480986403</v>
       </c>
       <c r="P8" t="n">
-        <v>421.7171283879653</v>
+        <v>421.8578326444159</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -12049,28 +12141,28 @@
         <v>0.035</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4096509820074042</v>
+        <v>-0.4199568761752955</v>
       </c>
       <c r="J9" t="n">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="K9" t="n">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="L9" t="n">
-        <v>0.154051085680016</v>
+        <v>0.1623641745381234</v>
       </c>
       <c r="M9" t="n">
-        <v>5.698078299992304</v>
+        <v>5.712012328549072</v>
       </c>
       <c r="N9" t="n">
-        <v>55.09506005334259</v>
+        <v>54.96524359519255</v>
       </c>
       <c r="O9" t="n">
-        <v>7.422604667725649</v>
+        <v>7.413854840445188</v>
       </c>
       <c r="P9" t="n">
-        <v>406.2473947282251</v>
+        <v>406.3459475685582</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -12112,7 +12204,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J235"/>
+  <dimension ref="A1:J237"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24323,6 +24415,110 @@
         </is>
       </c>
     </row>
+    <row r="236">
+      <c r="A236" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:17:51+00:00</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>-35.17729588502188,173.1179709592317</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>-35.17792705649666,173.11848349030856</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>-35.17827451261817,173.1192805615877</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>-35.17852592886158,173.12009407665556</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>-35.17870072885001,173.12088605957106</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>-35.17878947530374,173.1217286026835</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>-35.178808805709615,173.122595150293</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>-35.17875682133284,173.1234673894765</t>
+        </is>
+      </c>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-14 22:17:57+00:00</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>-35.177294888410685,173.11797207298736</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>-35.177946347779674,173.1184626449668</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>-35.17827236957754,173.119282386696</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>-35.17852165309428,173.1200964206707</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>-35.1786985279086,173.12088665336358</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>-35.17879586311902,173.1217280805371</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>-35.17882007045591,173.12259562376104</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>-35.17876202650094,173.1234680088939</t>
+        </is>
+      </c>
+      <c r="J237" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0061/nzd0061.xlsx
+++ b/data/nzd0061/nzd0061.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J237"/>
+  <dimension ref="A1:J239"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8968,6 +8968,78 @@
         <v>388.79</v>
       </c>
       <c r="J237" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:18:00+00:00</t>
+        </is>
+      </c>
+      <c r="B238" t="n">
+        <v>375.5</v>
+      </c>
+      <c r="C238" t="n">
+        <v>355.6</v>
+      </c>
+      <c r="D238" t="n">
+        <v>375.81</v>
+      </c>
+      <c r="E238" t="n">
+        <v>387.57</v>
+      </c>
+      <c r="F238" t="n">
+        <v>391.87</v>
+      </c>
+      <c r="G238" t="n">
+        <v>389.63</v>
+      </c>
+      <c r="H238" t="n">
+        <v>388.93</v>
+      </c>
+      <c r="I238" t="n">
+        <v>386.49</v>
+      </c>
+      <c r="J238" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-15 22:17:55+00:00</t>
+        </is>
+      </c>
+      <c r="B239" t="n">
+        <v>373.52</v>
+      </c>
+      <c r="C239" t="n">
+        <v>355</v>
+      </c>
+      <c r="D239" t="n">
+        <v>375.49</v>
+      </c>
+      <c r="E239" t="n">
+        <v>387.27</v>
+      </c>
+      <c r="F239" t="n">
+        <v>391.8</v>
+      </c>
+      <c r="G239" t="n">
+        <v>389.2</v>
+      </c>
+      <c r="H239" t="n">
+        <v>388.11</v>
+      </c>
+      <c r="I239" t="n">
+        <v>385.96</v>
+      </c>
+      <c r="J239" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -8984,7 +9056,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B244"/>
+  <dimension ref="A1:B246"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11427,6 +11499,26 @@
       </c>
       <c r="B244" t="n">
         <v>-0.54</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B245" t="n">
+        <v>-0.57</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>2026-01-15 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B246" t="n">
+        <v>0.24</v>
       </c>
     </row>
   </sheetData>
@@ -11595,28 +11687,28 @@
         <v>0.0315</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.326177771598281</v>
+        <v>-1.33728160996041</v>
       </c>
       <c r="J2" t="n">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="K2" t="n">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3044262312612459</v>
+        <v>0.3115540699692835</v>
       </c>
       <c r="M2" t="n">
-        <v>11.72124461491661</v>
+        <v>11.67450552154036</v>
       </c>
       <c r="N2" t="n">
-        <v>242.7606781941014</v>
+        <v>241.1316604751091</v>
       </c>
       <c r="O2" t="n">
-        <v>15.58077912667083</v>
+        <v>15.52841461563637</v>
       </c>
       <c r="P2" t="n">
-        <v>416.532245236909</v>
+        <v>416.6388277004188</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -11673,28 +11765,28 @@
         <v>0.0697</v>
       </c>
       <c r="I3" t="n">
-        <v>-2.277089737919934</v>
+        <v>-2.273792692357819</v>
       </c>
       <c r="J3" t="n">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="K3" t="n">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6457313463274553</v>
+        <v>0.6492382555881806</v>
       </c>
       <c r="M3" t="n">
-        <v>10.19532519965489</v>
+        <v>10.13347352504832</v>
       </c>
       <c r="N3" t="n">
-        <v>171.8521139668584</v>
+        <v>170.4440857437363</v>
       </c>
       <c r="O3" t="n">
-        <v>13.10923773401255</v>
+        <v>13.05542361410522</v>
       </c>
       <c r="P3" t="n">
-        <v>413.3108815021964</v>
+        <v>413.2792426708305</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -11751,28 +11843,28 @@
         <v>0.0522</v>
       </c>
       <c r="I4" t="n">
-        <v>-2.268530472534846</v>
+        <v>-2.261545953275942</v>
       </c>
       <c r="J4" t="n">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="K4" t="n">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6708506558472733</v>
+        <v>0.6733300645780103</v>
       </c>
       <c r="M4" t="n">
-        <v>9.716271808212191</v>
+        <v>9.678457373697546</v>
       </c>
       <c r="N4" t="n">
-        <v>152.0186725784402</v>
+        <v>150.8950387735084</v>
       </c>
       <c r="O4" t="n">
-        <v>12.32958525573509</v>
+        <v>12.28393417328131</v>
       </c>
       <c r="P4" t="n">
-        <v>431.1205356913031</v>
+        <v>431.0532117353011</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -11829,28 +11921,28 @@
         <v>0.0455</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.97736656639898</v>
+        <v>-1.97792453112716</v>
       </c>
       <c r="J5" t="n">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="K5" t="n">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6383976268454881</v>
+        <v>0.6427787892688989</v>
       </c>
       <c r="M5" t="n">
-        <v>8.939657317518376</v>
+        <v>8.866759570624195</v>
       </c>
       <c r="N5" t="n">
-        <v>133.3383072682641</v>
+        <v>132.2142000309701</v>
       </c>
       <c r="O5" t="n">
-        <v>11.54722075948425</v>
+        <v>11.49844337425593</v>
       </c>
       <c r="P5" t="n">
-        <v>439.9629464957616</v>
+        <v>439.9683265996035</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -11907,28 +11999,28 @@
         <v>0.0311</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.533107403349669</v>
+        <v>-1.542753581380423</v>
       </c>
       <c r="J6" t="n">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="K6" t="n">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5486934645113961</v>
+        <v>0.5557141587503549</v>
       </c>
       <c r="M6" t="n">
-        <v>8.328084901891518</v>
+        <v>8.312246048779063</v>
       </c>
       <c r="N6" t="n">
-        <v>116.7886736035045</v>
+        <v>116.1117637078009</v>
       </c>
       <c r="O6" t="n">
-        <v>10.80688084525338</v>
+        <v>10.77551686499543</v>
       </c>
       <c r="P6" t="n">
-        <v>438.3991181998614</v>
+        <v>438.4916956254443</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -11985,28 +12077,28 @@
         <v>0.0262</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.9636213816129865</v>
+        <v>-0.9758151341712958</v>
       </c>
       <c r="J7" t="n">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="K7" t="n">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3623751057025871</v>
+        <v>0.3713549262934631</v>
       </c>
       <c r="M7" t="n">
-        <v>7.682476198283732</v>
+        <v>7.688338219334896</v>
       </c>
       <c r="N7" t="n">
-        <v>98.70371396527656</v>
+        <v>98.36113020172863</v>
       </c>
       <c r="O7" t="n">
-        <v>9.934974281057629</v>
+        <v>9.917717993658048</v>
       </c>
       <c r="P7" t="n">
-        <v>422.5578729558416</v>
+        <v>422.6749034414804</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -12063,28 +12155,28 @@
         <v>0.0267</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.8480618515906057</v>
+        <v>-0.8654243903314293</v>
       </c>
       <c r="J8" t="n">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="K8" t="n">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2918674017891483</v>
+        <v>0.3022464971954617</v>
       </c>
       <c r="M8" t="n">
-        <v>7.446212350985872</v>
+        <v>7.496991513751841</v>
       </c>
       <c r="N8" t="n">
-        <v>105.750882515089</v>
+        <v>105.8455316877502</v>
       </c>
       <c r="O8" t="n">
-        <v>10.28352480986403</v>
+        <v>10.28812576166087</v>
       </c>
       <c r="P8" t="n">
-        <v>421.8578326444159</v>
+        <v>422.0240263996346</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -12141,28 +12233,28 @@
         <v>0.035</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4199568761752955</v>
+        <v>-0.4342511005010674</v>
       </c>
       <c r="J9" t="n">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="K9" t="n">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1623641745381234</v>
+        <v>0.1725691183302617</v>
       </c>
       <c r="M9" t="n">
-        <v>5.712012328549072</v>
+        <v>5.75100912529773</v>
       </c>
       <c r="N9" t="n">
-        <v>54.96524359519255</v>
+        <v>55.17249008794677</v>
       </c>
       <c r="O9" t="n">
-        <v>7.413854840445188</v>
+        <v>7.427818662834114</v>
       </c>
       <c r="P9" t="n">
-        <v>406.3459475685582</v>
+        <v>406.4831379308059</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -12204,7 +12296,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J237"/>
+  <dimension ref="A1:J239"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24519,6 +24611,110 @@
         </is>
       </c>
     </row>
+    <row r="238">
+      <c r="A238" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:18:00+00:00</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>-35.17731581724353,173.11794868411297</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>-35.17794513364308,173.11846395691165</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>-35.17827658176081,173.11927879941408</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>-35.1785282311978,173.12009281449343</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>-35.17871050102978,173.120883423132</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>-35.17880297068812,173.12172749955715</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>-35.17883007355059,173.1225960442008</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>-35.1787826676847,173.12347046520512</t>
+        </is>
+      </c>
+      <c r="J238" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-15 22:17:55+00:00</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>-35.177328972507546,173.11793398252868</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>-35.17794918076498,173.1184595837619</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>-35.17827894649522,173.11927678550126</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>-35.17853069798661,173.12009146217682</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>-35.17871111729336,173.12088325687006</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>-35.17880683936496,173.12172718332752</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>-35.17883746322413,173.12259635479603</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>-35.1787874241314,173.1234710312248</t>
+        </is>
+      </c>
+      <c r="J239" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0061/nzd0061.xlsx
+++ b/data/nzd0061/nzd0061.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J239"/>
+  <dimension ref="A1:J240"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9042,6 +9042,42 @@
       <c r="J239" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-23 22:17:42+00:00</t>
+        </is>
+      </c>
+      <c r="B240" t="n">
+        <v>371.4</v>
+      </c>
+      <c r="C240" t="n">
+        <v>354.41</v>
+      </c>
+      <c r="D240" t="n">
+        <v>374.04</v>
+      </c>
+      <c r="E240" t="n">
+        <v>386.34</v>
+      </c>
+      <c r="F240" t="n">
+        <v>391.29</v>
+      </c>
+      <c r="G240" t="n">
+        <v>387.77</v>
+      </c>
+      <c r="H240" t="n">
+        <v>386.97</v>
+      </c>
+      <c r="I240" t="n">
+        <v>384</v>
+      </c>
+      <c r="J240" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -9056,7 +9092,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B246"/>
+  <dimension ref="A1:B247"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11519,6 +11555,16 @@
       </c>
       <c r="B246" t="n">
         <v>0.24</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>2026-01-23 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B247" t="n">
+        <v>0.38</v>
       </c>
     </row>
   </sheetData>
@@ -11687,28 +11733,28 @@
         <v>0.0315</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.33728160996041</v>
+        <v>-1.345026234333087</v>
       </c>
       <c r="J2" t="n">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="K2" t="n">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3115540699692835</v>
+        <v>0.315629625151049</v>
       </c>
       <c r="M2" t="n">
-        <v>11.67450552154036</v>
+        <v>11.66226270500152</v>
       </c>
       <c r="N2" t="n">
-        <v>241.1316604751091</v>
+        <v>240.526604934008</v>
       </c>
       <c r="O2" t="n">
-        <v>15.52841461563637</v>
+        <v>15.50892017304906</v>
       </c>
       <c r="P2" t="n">
-        <v>416.6388277004188</v>
+        <v>416.7133118196825</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -11765,28 +11811,28 @@
         <v>0.0697</v>
       </c>
       <c r="I3" t="n">
-        <v>-2.273792692357819</v>
+        <v>-2.272822220887329</v>
       </c>
       <c r="J3" t="n">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="K3" t="n">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6492382555881806</v>
+        <v>0.6510974672768646</v>
       </c>
       <c r="M3" t="n">
-        <v>10.13347352504832</v>
+        <v>10.09803405970169</v>
       </c>
       <c r="N3" t="n">
-        <v>170.4440857437363</v>
+        <v>169.7372721824765</v>
       </c>
       <c r="O3" t="n">
-        <v>13.05542361410522</v>
+        <v>13.02832576283217</v>
       </c>
       <c r="P3" t="n">
-        <v>413.2792426708305</v>
+        <v>413.2699091371081</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -11843,28 +11889,28 @@
         <v>0.0522</v>
       </c>
       <c r="I4" t="n">
-        <v>-2.261545953275942</v>
+        <v>-2.259364158692528</v>
       </c>
       <c r="J4" t="n">
+        <v>239</v>
+      </c>
+      <c r="K4" t="n">
         <v>238</v>
       </c>
-      <c r="K4" t="n">
-        <v>237</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.6733300645780103</v>
+        <v>0.6748507061556959</v>
       </c>
       <c r="M4" t="n">
-        <v>9.678457373697546</v>
+        <v>9.651487477850836</v>
       </c>
       <c r="N4" t="n">
-        <v>150.8950387735084</v>
+        <v>150.2929705883263</v>
       </c>
       <c r="O4" t="n">
-        <v>12.28393417328131</v>
+        <v>12.25940335368432</v>
       </c>
       <c r="P4" t="n">
-        <v>431.0532117353011</v>
+        <v>431.0321365424804</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -11921,28 +11967,28 @@
         <v>0.0455</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.97792453112716</v>
+        <v>-1.97898061734345</v>
       </c>
       <c r="J5" t="n">
+        <v>239</v>
+      </c>
+      <c r="K5" t="n">
         <v>238</v>
       </c>
-      <c r="K5" t="n">
-        <v>237</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.6427787892688989</v>
+        <v>0.6450889029132445</v>
       </c>
       <c r="M5" t="n">
-        <v>8.866759570624195</v>
+        <v>8.83431586352782</v>
       </c>
       <c r="N5" t="n">
-        <v>132.2142000309701</v>
+        <v>131.6661627761592</v>
       </c>
       <c r="O5" t="n">
-        <v>11.49844337425593</v>
+        <v>11.47458769525769</v>
       </c>
       <c r="P5" t="n">
-        <v>439.9683265996035</v>
+        <v>439.9785279360688</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -11999,28 +12045,28 @@
         <v>0.0311</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.542753581380423</v>
+        <v>-1.547778125310561</v>
       </c>
       <c r="J6" t="n">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="K6" t="n">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5557141587503549</v>
+        <v>0.5591924504556998</v>
       </c>
       <c r="M6" t="n">
-        <v>8.312246048779063</v>
+        <v>8.305692205099584</v>
       </c>
       <c r="N6" t="n">
-        <v>116.1117637078009</v>
+        <v>115.7959319365704</v>
       </c>
       <c r="O6" t="n">
-        <v>10.77551686499543</v>
+        <v>10.76085182207108</v>
       </c>
       <c r="P6" t="n">
-        <v>438.4916956254443</v>
+        <v>438.5400193027886</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -12077,28 +12123,28 @@
         <v>0.0262</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.9758151341712958</v>
+        <v>-0.9829478671235098</v>
       </c>
       <c r="J7" t="n">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="K7" t="n">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3713549262934631</v>
+        <v>0.3760686520603418</v>
       </c>
       <c r="M7" t="n">
-        <v>7.688338219334896</v>
+        <v>7.698595341423609</v>
       </c>
       <c r="N7" t="n">
-        <v>98.36113020172863</v>
+        <v>98.29214462027021</v>
       </c>
       <c r="O7" t="n">
-        <v>9.917717993658048</v>
+        <v>9.914239487740359</v>
       </c>
       <c r="P7" t="n">
-        <v>422.6749034414804</v>
+        <v>422.7435026796517</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -12155,28 +12201,28 @@
         <v>0.0267</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.8654243903314293</v>
+        <v>-0.8749828451496807</v>
       </c>
       <c r="J8" t="n">
+        <v>239</v>
+      </c>
+      <c r="K8" t="n">
         <v>238</v>
       </c>
-      <c r="K8" t="n">
-        <v>237</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.3022464971954617</v>
+        <v>0.3075981355651847</v>
       </c>
       <c r="M8" t="n">
-        <v>7.496991513751841</v>
+        <v>7.52833082937499</v>
       </c>
       <c r="N8" t="n">
-        <v>105.8455316877502</v>
+        <v>106.0156960413887</v>
       </c>
       <c r="O8" t="n">
-        <v>10.28812576166087</v>
+        <v>10.29639237992554</v>
       </c>
       <c r="P8" t="n">
-        <v>422.0240263996346</v>
+        <v>422.1157094234191</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -12233,28 +12279,28 @@
         <v>0.035</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4342511005010674</v>
+        <v>-0.4428672915406588</v>
       </c>
       <c r="J9" t="n">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="K9" t="n">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1725691183302617</v>
+        <v>0.1782535128699568</v>
       </c>
       <c r="M9" t="n">
-        <v>5.75100912529773</v>
+        <v>5.778992645778496</v>
       </c>
       <c r="N9" t="n">
-        <v>55.17249008794677</v>
+        <v>55.44152147829803</v>
       </c>
       <c r="O9" t="n">
-        <v>7.427818662834114</v>
+        <v>7.44590635707286</v>
       </c>
       <c r="P9" t="n">
-        <v>406.4831379308059</v>
+        <v>406.5660043643614</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -12296,7 +12342,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J239"/>
+  <dimension ref="A1:J240"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24715,6 +24761,58 @@
         </is>
       </c>
     </row>
+    <row r="240">
+      <c r="A240" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-23 22:17:42+00:00</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>-35.177343057939744,173.11791824143313</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>-35.17795316043468,173.11845528349755</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>-35.17828966169758,173.11926765995733</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>-35.17853834503176,173.12008726999474</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>-35.17871560721377,173.12088204553297</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>-35.17881970496466,173.12172613167996</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>-35.17884773667269,173.12259678659922</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>-35.17880501400962,173.12347312443038</t>
+        </is>
+      </c>
+      <c r="J240" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0061/nzd0061.xlsx
+++ b/data/nzd0061/nzd0061.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J240"/>
+  <dimension ref="A1:J241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9078,6 +9078,42 @@
       <c r="J240" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-20 22:17:31+00:00</t>
+        </is>
+      </c>
+      <c r="B241" t="n">
+        <v>371.96</v>
+      </c>
+      <c r="C241" t="n">
+        <v>355.24</v>
+      </c>
+      <c r="D241" t="n">
+        <v>374.77</v>
+      </c>
+      <c r="E241" t="n">
+        <v>388.71</v>
+      </c>
+      <c r="F241" t="n">
+        <v>395.21</v>
+      </c>
+      <c r="G241" t="n">
+        <v>387.01</v>
+      </c>
+      <c r="H241" t="n">
+        <v>387.36</v>
+      </c>
+      <c r="I241" t="n">
+        <v>384.14</v>
+      </c>
+      <c r="J241" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -9092,7 +9128,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B247"/>
+  <dimension ref="A1:B248"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11565,6 +11601,16 @@
       </c>
       <c r="B247" t="n">
         <v>0.38</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>2026-03-20 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B248" t="n">
+        <v>1.53</v>
       </c>
     </row>
   </sheetData>
@@ -11733,28 +11779,28 @@
         <v>0.0315</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.345026234333087</v>
+        <v>-1.352065002551546</v>
       </c>
       <c r="J2" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="K2" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L2" t="n">
-        <v>0.315629625151049</v>
+        <v>0.3195742951207932</v>
       </c>
       <c r="M2" t="n">
-        <v>11.66226270500152</v>
+        <v>11.64659739555613</v>
       </c>
       <c r="N2" t="n">
-        <v>240.526604934008</v>
+        <v>239.8566344421872</v>
       </c>
       <c r="O2" t="n">
-        <v>15.50892017304906</v>
+        <v>15.48730559013372</v>
       </c>
       <c r="P2" t="n">
-        <v>416.7133118196825</v>
+        <v>416.781503183939</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -11811,28 +11857,28 @@
         <v>0.0697</v>
       </c>
       <c r="I3" t="n">
-        <v>-2.272822220887329</v>
+        <v>-2.270942926831308</v>
       </c>
       <c r="J3" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="K3" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6510974672768646</v>
+        <v>0.6527660813783632</v>
       </c>
       <c r="M3" t="n">
-        <v>10.09803405970169</v>
+        <v>10.0692350167059</v>
       </c>
       <c r="N3" t="n">
-        <v>169.7372721824765</v>
+        <v>169.0537160053099</v>
       </c>
       <c r="O3" t="n">
-        <v>13.02832576283217</v>
+        <v>13.00206583606274</v>
       </c>
       <c r="P3" t="n">
-        <v>413.2699091371081</v>
+        <v>413.2517025956307</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -11889,28 +11935,28 @@
         <v>0.0522</v>
       </c>
       <c r="I4" t="n">
-        <v>-2.259364158692528</v>
+        <v>-2.256362037787802</v>
       </c>
       <c r="J4" t="n">
+        <v>240</v>
+      </c>
+      <c r="K4" t="n">
         <v>239</v>
       </c>
-      <c r="K4" t="n">
-        <v>238</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.6748507061556959</v>
+        <v>0.6761847736947888</v>
       </c>
       <c r="M4" t="n">
-        <v>9.651487477850836</v>
+        <v>9.629650828085706</v>
       </c>
       <c r="N4" t="n">
-        <v>150.2929705883263</v>
+        <v>149.7243568402346</v>
       </c>
       <c r="O4" t="n">
-        <v>12.25940335368432</v>
+        <v>12.23619045455875</v>
       </c>
       <c r="P4" t="n">
-        <v>431.0321365424804</v>
+        <v>431.0029249752097</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -11967,28 +12013,28 @@
         <v>0.0455</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.97898061734345</v>
+        <v>-1.977920075871754</v>
       </c>
       <c r="J5" t="n">
+        <v>240</v>
+      </c>
+      <c r="K5" t="n">
         <v>239</v>
       </c>
-      <c r="K5" t="n">
-        <v>238</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.6450889029132445</v>
+        <v>0.6469225749714962</v>
       </c>
       <c r="M5" t="n">
-        <v>8.83431586352782</v>
+        <v>8.803755916097018</v>
       </c>
       <c r="N5" t="n">
-        <v>131.6661627761592</v>
+        <v>131.1227744050826</v>
       </c>
       <c r="O5" t="n">
-        <v>11.47458769525769</v>
+        <v>11.45088531097411</v>
       </c>
       <c r="P5" t="n">
-        <v>439.9785279360688</v>
+        <v>439.9682085387071</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -12045,28 +12091,28 @@
         <v>0.0311</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.547778125310561</v>
+        <v>-1.549477429623146</v>
       </c>
       <c r="J6" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="K6" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5591924504556998</v>
+        <v>0.5619451009767652</v>
       </c>
       <c r="M6" t="n">
-        <v>8.305692205099584</v>
+        <v>8.280486832780522</v>
       </c>
       <c r="N6" t="n">
-        <v>115.7959319365704</v>
+        <v>115.3328121966818</v>
       </c>
       <c r="O6" t="n">
-        <v>10.76085182207108</v>
+        <v>10.7393115327139</v>
       </c>
       <c r="P6" t="n">
-        <v>438.5400193027886</v>
+        <v>438.5564821093147</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -12123,28 +12169,28 @@
         <v>0.0262</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.9829478671235098</v>
+        <v>-0.9904635891301297</v>
       </c>
       <c r="J7" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="K7" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3760686520603418</v>
+        <v>0.3808955372297327</v>
       </c>
       <c r="M7" t="n">
-        <v>7.698595341423609</v>
+        <v>7.710479632228117</v>
       </c>
       <c r="N7" t="n">
-        <v>98.29214462027021</v>
+        <v>98.26136673682787</v>
       </c>
       <c r="O7" t="n">
-        <v>9.914239487740359</v>
+        <v>9.912687160242063</v>
       </c>
       <c r="P7" t="n">
-        <v>422.7435026796517</v>
+        <v>422.8163147571485</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -12201,28 +12247,28 @@
         <v>0.0267</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.8749828451496807</v>
+        <v>-0.8839971402073126</v>
       </c>
       <c r="J8" t="n">
+        <v>240</v>
+      </c>
+      <c r="K8" t="n">
         <v>239</v>
       </c>
-      <c r="K8" t="n">
-        <v>238</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.3075981355651847</v>
+        <v>0.3128479345646198</v>
       </c>
       <c r="M8" t="n">
-        <v>7.52833082937499</v>
+        <v>7.555691109603815</v>
       </c>
       <c r="N8" t="n">
-        <v>106.0156960413887</v>
+        <v>106.1167984597438</v>
       </c>
       <c r="O8" t="n">
-        <v>10.29639237992554</v>
+        <v>10.30130081396247</v>
       </c>
       <c r="P8" t="n">
-        <v>422.1157094234191</v>
+        <v>422.2028083001618</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -12279,28 +12325,28 @@
         <v>0.035</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4428672915406588</v>
+        <v>-0.4512056488374659</v>
       </c>
       <c r="J9" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="K9" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1782535128699568</v>
+        <v>0.1838946792760903</v>
       </c>
       <c r="M9" t="n">
-        <v>5.778992645778496</v>
+        <v>5.8044794247542</v>
       </c>
       <c r="N9" t="n">
-        <v>55.44152147829803</v>
+        <v>55.67674305816825</v>
       </c>
       <c r="O9" t="n">
-        <v>7.44590635707286</v>
+        <v>7.461685001269368</v>
       </c>
       <c r="P9" t="n">
-        <v>406.5660043643614</v>
+        <v>406.6467861065755</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -12342,7 +12388,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J240"/>
+  <dimension ref="A1:J241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24813,6 +24859,58 @@
         </is>
       </c>
     </row>
+    <row r="241">
+      <c r="A241" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-20 22:17:31+00:00</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>-35.17733933725975,173.1179223994589</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>-35.177947561916234,173.11846133302186</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>-35.178284267147525,173.119272254197</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>-35.178518857400256,173.12009795329587</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>-35.17868109645259,173.12089135619902</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>-35.178826542626034,173.12172557276224</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>-35.178844222071874,173.12259663887707</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>-35.178803757589755,173.12347297491567</t>
+        </is>
+      </c>
+      <c r="J241" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0061/nzd0061.xlsx
+++ b/data/nzd0061/nzd0061.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J241"/>
+  <dimension ref="A1:J243"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9103,17 +9103,89 @@
         <v>395.21</v>
       </c>
       <c r="G241" t="n">
-        <v>387.01</v>
+        <v>390.83</v>
       </c>
       <c r="H241" t="n">
-        <v>387.36</v>
+        <v>390.96</v>
       </c>
       <c r="I241" t="n">
-        <v>384.14</v>
+        <v>387.14</v>
       </c>
       <c r="J241" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:17:05+00:00</t>
+        </is>
+      </c>
+      <c r="B242" t="n">
+        <v>371.75</v>
+      </c>
+      <c r="C242" t="n">
+        <v>355.02</v>
+      </c>
+      <c r="D242" t="n">
+        <v>374.93</v>
+      </c>
+      <c r="E242" t="n">
+        <v>389.3</v>
+      </c>
+      <c r="F242" t="n">
+        <v>396.28</v>
+      </c>
+      <c r="G242" t="n">
+        <v>392.02</v>
+      </c>
+      <c r="H242" t="n">
+        <v>391.83</v>
+      </c>
+      <c r="I242" t="n">
+        <v>388.27</v>
+      </c>
+      <c r="J242" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:16:42+00:00</t>
+        </is>
+      </c>
+      <c r="B243" t="n">
+        <v>371.2</v>
+      </c>
+      <c r="C243" t="n">
+        <v>355.4</v>
+      </c>
+      <c r="D243" t="n">
+        <v>375.26</v>
+      </c>
+      <c r="E243" t="n">
+        <v>389.82</v>
+      </c>
+      <c r="F243" t="n">
+        <v>397.36</v>
+      </c>
+      <c r="G243" t="n">
+        <v>392.81</v>
+      </c>
+      <c r="H243" t="n">
+        <v>392.72</v>
+      </c>
+      <c r="I243" t="n">
+        <v>389.65</v>
+      </c>
+      <c r="J243" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -9128,7 +9200,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B248"/>
+  <dimension ref="A1:B250"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11611,6 +11683,26 @@
       </c>
       <c r="B248" t="n">
         <v>1.53</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B249" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B250" t="n">
+        <v>0.76</v>
       </c>
     </row>
   </sheetData>
@@ -11779,28 +11871,28 @@
         <v>0.0315</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.352065002551546</v>
+        <v>-1.366222708756553</v>
       </c>
       <c r="J2" t="n">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="K2" t="n">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3195742951207932</v>
+        <v>0.3275000530448505</v>
       </c>
       <c r="M2" t="n">
-        <v>11.64659739555613</v>
+        <v>11.61506564935196</v>
       </c>
       <c r="N2" t="n">
-        <v>239.8566344421872</v>
+        <v>238.5528932718266</v>
       </c>
       <c r="O2" t="n">
-        <v>15.48730559013372</v>
+        <v>15.4451575994493</v>
       </c>
       <c r="P2" t="n">
-        <v>416.781503183939</v>
+        <v>416.9195117666259</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -11857,28 +11949,28 @@
         <v>0.0697</v>
       </c>
       <c r="I3" t="n">
-        <v>-2.270942926831308</v>
+        <v>-2.266872895830121</v>
       </c>
       <c r="J3" t="n">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="K3" t="n">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6527660813783632</v>
+        <v>0.6560014802825231</v>
       </c>
       <c r="M3" t="n">
-        <v>10.0692350167059</v>
+        <v>10.01426379214783</v>
       </c>
       <c r="N3" t="n">
-        <v>169.0537160053099</v>
+        <v>167.7130677693598</v>
       </c>
       <c r="O3" t="n">
-        <v>13.00206583606274</v>
+        <v>12.95040801555533</v>
       </c>
       <c r="P3" t="n">
-        <v>413.2517025956307</v>
+        <v>413.2120255514411</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -11935,28 +12027,28 @@
         <v>0.0522</v>
       </c>
       <c r="I4" t="n">
-        <v>-2.256362037787802</v>
+        <v>-2.249569833538176</v>
       </c>
       <c r="J4" t="n">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="K4" t="n">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6761847736947888</v>
+        <v>0.678621714339853</v>
       </c>
       <c r="M4" t="n">
-        <v>9.629650828085706</v>
+        <v>9.590926008955158</v>
       </c>
       <c r="N4" t="n">
-        <v>149.7243568402346</v>
+        <v>148.6377168748573</v>
       </c>
       <c r="O4" t="n">
-        <v>12.23619045455875</v>
+        <v>12.19170688931034</v>
       </c>
       <c r="P4" t="n">
-        <v>431.0029249752097</v>
+        <v>430.936424094609</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -12013,28 +12105,28 @@
         <v>0.0455</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.977920075871754</v>
+        <v>-1.974133369035521</v>
       </c>
       <c r="J5" t="n">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="K5" t="n">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6469225749714962</v>
+        <v>0.6501184533063897</v>
       </c>
       <c r="M5" t="n">
-        <v>8.803755916097018</v>
+        <v>8.753323729859796</v>
       </c>
       <c r="N5" t="n">
-        <v>131.1227744050826</v>
+        <v>130.0836793396882</v>
       </c>
       <c r="O5" t="n">
-        <v>11.45088531097411</v>
+        <v>11.40542324246181</v>
       </c>
       <c r="P5" t="n">
-        <v>439.9682085387071</v>
+        <v>439.9311309752408</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -12091,28 +12183,28 @@
         <v>0.0311</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.549477429623146</v>
+        <v>-1.549989913759034</v>
       </c>
       <c r="J6" t="n">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="K6" t="n">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5619451009767652</v>
+        <v>0.5665821322734295</v>
       </c>
       <c r="M6" t="n">
-        <v>8.280486832780522</v>
+        <v>8.216902683243323</v>
       </c>
       <c r="N6" t="n">
-        <v>115.3328121966818</v>
+        <v>114.383265243695</v>
       </c>
       <c r="O6" t="n">
-        <v>10.7393115327139</v>
+        <v>10.6950112315834</v>
       </c>
       <c r="P6" t="n">
-        <v>438.5564821093147</v>
+        <v>438.5614686932421</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -12169,28 +12261,28 @@
         <v>0.0262</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.9904635891301297</v>
+        <v>-0.9936168036504008</v>
       </c>
       <c r="J7" t="n">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="K7" t="n">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3808955372297327</v>
+        <v>0.3869790120272492</v>
       </c>
       <c r="M7" t="n">
-        <v>7.710479632228117</v>
+        <v>7.664722094320311</v>
       </c>
       <c r="N7" t="n">
-        <v>98.26136673682787</v>
+        <v>97.33893634826011</v>
       </c>
       <c r="O7" t="n">
-        <v>9.912687160242063</v>
+        <v>9.866049683042352</v>
       </c>
       <c r="P7" t="n">
-        <v>422.8163147571485</v>
+        <v>422.8472235235579</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -12247,28 +12339,28 @@
         <v>0.0267</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.8839971402073126</v>
+        <v>-0.8909900039871413</v>
       </c>
       <c r="J8" t="n">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="K8" t="n">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3128479345646198</v>
+        <v>0.3201269248943674</v>
       </c>
       <c r="M8" t="n">
-        <v>7.555691109603815</v>
+        <v>7.537844532030602</v>
       </c>
       <c r="N8" t="n">
-        <v>106.1167984597438</v>
+        <v>105.2785219319838</v>
       </c>
       <c r="O8" t="n">
-        <v>10.30130081396247</v>
+        <v>10.2605322440887</v>
       </c>
       <c r="P8" t="n">
-        <v>422.2028083001618</v>
+        <v>422.2709548581068</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -12325,28 +12417,28 @@
         <v>0.035</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4512056488374659</v>
+        <v>-0.4575989120278776</v>
       </c>
       <c r="J9" t="n">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="K9" t="n">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1838946792760903</v>
+        <v>0.1908472444369351</v>
       </c>
       <c r="M9" t="n">
-        <v>5.8044794247542</v>
+        <v>5.793686894345407</v>
       </c>
       <c r="N9" t="n">
-        <v>55.67674305816825</v>
+        <v>55.25548550675587</v>
       </c>
       <c r="O9" t="n">
-        <v>7.461685001269368</v>
+        <v>7.433403359616366</v>
       </c>
       <c r="P9" t="n">
-        <v>406.6467861065755</v>
+        <v>406.7092350262086</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -12388,7 +12480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J241"/>
+  <dimension ref="A1:J243"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24892,22 +24984,126 @@
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>-35.178826542626034,173.12172557276224</t>
+          <t>-35.17879217438064,173.12172838205828</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>-35.178844222071874,173.12259663887707</t>
+          <t>-35.17881177960265,173.12259527528855</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>-35.178803757589755,173.12347297491567</t>
+          <t>-35.1787768343067,173.12346977103007</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:17:05+00:00</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>-35.17734073251477,173.11792084019928</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>-35.177949045860906,173.11845972953358</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>-35.178283084780354,173.11927326115352</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>-35.178514006048786,173.12010061285108</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>-35.178671676423235,173.12089389762946</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>-35.17878146804235,173.121729257205</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>-35.17880393933921,173.12259494575483</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>-35.17876669320337,173.1234685642337</t>
+        </is>
+      </c>
+      <c r="J242" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:16:42+00:00</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>-35.177344386754,173.11791675642382</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>-35.17794648268374,173.11846249919512</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>-35.17828064614805,173.11927533800133</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>-35.17850973028135,173.12010295686554</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>-35.17866216835617,173.120896462811</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>-35.17877436047323,173.12172983818465</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>-35.17879591883983,173.12259460864567</t>
+        </is>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>-35.178754308493055,173.12346709044743</t>
+        </is>
+      </c>
+      <c r="J243" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
